--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P252"/>
+  <dimension ref="A1:P258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15996,7 +15996,6 @@
           <t>TC 0건 + 시트 분리</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
           <t>기능</t>
@@ -16020,14 +16019,11 @@
 2. 파일에 "Test Cases" 시트 한 장이 있고 헤더가 있다.</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
         <is>
           <t>높음</t>
@@ -16065,7 +16061,6 @@
           <t>시트명 31자 초과</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
           <t>기능</t>
@@ -16089,14 +16084,11 @@
 3. 엑셀이 복구 경고 없이 파일을 연다.</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
           <t>중간</t>
@@ -16134,7 +16126,6 @@
           <t>엑셀 금지 문자 시트명</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
           <t>기능</t>
@@ -16157,20 +16148,396 @@
 2. 탭 이름이 비어 있지 않다.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>225</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TC-RPT-010</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>실패·차단 항목</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>BLOCK 상세</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>BLOCK 결과가 1건 이상 있고 FAIL 은 없는 런</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 해당 런을 선택한다.
+2. 실패·차단 항목 표를 본다.
+3. PDF 를 받아 Failed / Blocked Test Cases 절을 본다.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>1. BLOCK 인 TC 가 결과 BLOCK 으로, 실제 결과와 함께 표시된다.
+2. '실패하거나 차단된 항목이 없습니다' 문구가 나오지 않는다.
+3. PDF 에도 [BLOCK] 항목이 실린다.</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>226</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TC-RPT-011</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>요약 표 폭</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>런 1개 이상 존재</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>1. PDF 를 받는다.
+2. Summary 표의 마지막 칸을 본다.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>1. Pass Rate 머리글과 값(예: 92.0%)이 페이지 안에 온전히 보인다.
+2. 제목과 머리행이 굵게 나온다.
+3. Version 이 비어 있으면 N/A 로 나온다.</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>227</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TC-RPT-012</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>다운로드</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>파일 이름</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>프로젝트 이름에 한글이 있는 런</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>1. PDF 다운로드를 누른다.
+2. Excel 다운로드를 누른다.</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>1. 파일 이름이 '프로젝트명_Report_R라운드.pdf/.xlsx' 다.
+2. report_번호 모양이 아니다.</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>228</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TC-RPT-013</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>우선순위별/분류별 합격률</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>우선순위가 둘 이상이고 우선순위를 비운 TC 가 있는 런</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 우선순위별 요약과 카테고리별 요약을 본다.
+2. Excel 을 받아 Summary 시트를 본다.</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>1. 우선순위가 높은 것부터 나열되고 빈 우선순위는 (미지정) 한 줄로 모인다.
+2. 합격률 분모는 PASS+FAIL+BLOCK 이고, 수행이 없으면 - 다.
+3. 엑셀 합격률 칸은 숫자이고 % 서식이다.</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>229</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TC-RPT-014</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>직전 수행 대비</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>회귀/해결</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>같은 프로젝트에 런 2개. 앞 런 PASS 였던 TC 가 뒤 런에서 FAIL, 앞 런 FAIL 이 뒤 런에서 PASS</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>1. 뒤 런의 리포트를 연다.
+2. 직전 수행 대비 섹션을 본다.
+3. 비교 탭에서 같은 두 런을 비교한다.</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>1. 회귀 1, 해결 1 과 해당 TC ID 가 표시된다.
+2. 비교 탭의 회귀/개선 건수와 같다.
+3. 첫 런의 리포트에는 이 섹션이 없다.</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>230</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TC-RPT-015</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>이슈 링크</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Jira 이슈 키</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>프로젝트 설정에 Jira Base URL 이 있고, 결과 이슈 링크에 PROJ-1 같은 키와 일반 메모가 적힌 런</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 실패·차단 항목과 연관 Jira 이슈를 본다.
+2. 이슈 키를 누른다.</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>1. 이슈 키는 Base URL/browse/키 로 열린다.
+2. 키 모양이 아닌 메모는 링크 없이 글자로만 나온다.
+3. href='#' 링크가 없다.</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P258"/>
+  <dimension ref="A1:P262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -16538,6 +16538,259 @@
         </is>
       </c>
       <c r="P258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>231</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TC-TREE-008</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>시트 트리</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>초기 선택</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>시트 여럿</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>시트가 2개 이상인 프로젝트</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>1. 다른 탭에서 TC 관리 탭을 누른다.
+2. 사이드바 활성 항목과 표의 TC 를 본다.
+3. 다른 시트를 빠르게 여러 번 바꿔 누른다.</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>1. 사이드바는 '전체' 가 활성이고 표에 모든 시트의 TC 가 나온다.
+2. 시트를 바꿀 때마다 표가 활성 시트의 TC 만 보여 준다.
+3. 활성 항목과 표의 범위가 어긋나지 않는다.</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>232</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TC-TREE-009</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>시트 트리</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>초기 선택</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>시트 하나</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>시트가 1개인 프로젝트 또는 시트를 지워 하나만 남은 프로젝트</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>1. TC 관리 탭을 연다.
+2. 행 추가 버튼을 본다.</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>1. 남은 시트가 자동으로 선택된다.
+2. 행 추가 버튼이 켜져 있다.</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>233</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TC-RUN-022</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>그리드</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>우선순위 색</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>우선순위가 매우 높음/높음/보통/낮음인 TC 가 있는 런</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>1. 테스트 수행에서 런을 연다.
+2. Priority 칸을 TC 관리 화면과 비교한다.
+3. EN 으로 바꿔 칸과 우선순위 필터 메뉴를 본다.</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>1. 네 값이 TC 관리와 같은 색으로 보인다.
+2. EN 에서 칸과 필터 메뉴가 같은 표시 이름(Critical/High/Normal/Low)이다.</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>234</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TC-SET-010</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>프로젝트 정보</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>이슈 관리 도구 주소</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>관리자 권한 프로젝트</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>1. 설정 탭에서 이슈 관리 도구 주소에 https://linear.app/워크스페이스 를 넣고 저장한다.
+2. 결과 이슈 링크가 PROJ-1 인 런의 리포트를 연다.
+3. 이슈 키를 누른다.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>1. 저장 후 다시 열어도 값이 남아 있다.
+2. 링크가 https://linear.app/워크스페이스/issue/PROJ-1 이다.
+3. 화면에 Jira Base URL 표기가 없다.</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P262"/>
+  <dimension ref="A1:P263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -16791,6 +16791,74 @@
         </is>
       </c>
       <c r="P262" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>235</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TC-RUN-023</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>그리드</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>이슈 링크 열기</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>설정 탭에 이슈 관리 도구 주소가 있는 프로젝트의 런</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1. Issue Link 칸에 PROJ-1 을 적는다.
+2. 칸 옆의 ↗ 를 누른다.
+3. ↗ 를 더블클릭한다.
+4. 글자를 더블클릭한 뒤 Escape 를 누른다.
+5. Issue Link 칸에 '재현 안 됨' 을 적는다.</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>1. 칸에 PROJ-1 과 ↗ 가 보인다.
+2. 이슈 관리 도구의 PROJ-1 이 새 탭 하나로 열린다.
+3. 편집기가 열리지 않고 새 탭도 하나만 열린다.
+4. 편집기가 열렸다가 원래 값으로 닫힌다.
+5. ↗ 가 붙지 않는다.</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P263"/>
+  <dimension ref="A1:P270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -16859,6 +16859,438 @@
         </is>
       </c>
       <c r="P263" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>236</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>TC-TR-043</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>첨부</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>큰 이미지 첨부</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>배포 환경(Vercel + Supabase). 5MB 이상 50MB 이하 이미지</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>1. 결과 행의 + 버튼으로 이미지를 고른다.
+2. 첨부 파일 이름을 눌러 미리보기를 연다.</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>1. "이미지 첨부 완료" 가 뜨고 파일 이름이 보인다.
+2. 미리보기 창에 이미지가 그려진다.</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>237</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>TC-TR-044</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>첨부</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>용량 초과 안내</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>50MB 를 넘는 이미지</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>1. + 버튼으로 50MB 를 넘는 이미지를 고른다.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>1. 서버에 올리기 전에 "파일이 너무 큽니다. 50MB 까지 올릴 수 있습니다." 가 뜬다.
+2. 첨부 목록은 그대로다.</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>238</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TC-TR-045</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>첨부</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>미리보기 실패</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>다른 사람이 방금 지운 첨부가 화면에 남아 있는 상태</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>1. 그 첨부 파일 이름을 누른다.</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>1. "이미지를 불러올 수 없습니다." 가 뜨고 미리보기 창이 닫힌다(깨진 이미지 창이 남지 않는다).</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>239</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TC-TR-046</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>결과 가져오기</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>미리보기 뒤 적용</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>TC ID 로 시작하는 테스트 이름이 든 JUnit XML</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>1. 결과 가져오기에서 파일을 고르고 미리보기를 누른다.
+2. 적용 버튼을 누른다.
+3. 같은 파일을 다시 골라 적용한다.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>1. 기록될 건수가 보인다.
+2. "결과 N건을 기록했습니다." 가 뜨고 그리드에 반영된다.
+3. 다시 적용해도 오류 없이 기록된다.</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>240</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TC-TCM-020</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TC 관리</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>가져오기</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>미리보기 뒤 가져오기</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>시트가 2개 이상인 엑셀 파일</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>1. Import 로 파일을 고른다.
+2. 시트 선택 창에서 가져오기를 누른다.
+3. 같은 파일을 다시 골라 가져온다.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>1. 시트 목록과 TC 수가 보인다.
+2. 시트별 신규/업데이트 수가 뜬다.
+3. 덮어쓰기 확인 뒤 업데이트 수가 뜬다.</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>241</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TC-ERR-011</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>에러 처리</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>동시 편집</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>잠금 대기 안내</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>같은 프로젝트를 두 탭에서 연 상태</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1. 두 탭에서 거의 동시에 TC 복제나 시트 이동을 한다.</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>1. 둘 다 반영되거나, 늦은 쪽에 "다른 작업이 진행 중입니다. 잠시 후 다시 시도해 주세요." 가 뜬다.
+2. TC 번호가 겹치거나 빠지지 않는다.</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>242</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TC-ADM-007</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>매뉴얼</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>API 문서</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>관리자 계정</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>1. 관리자 매뉴얼의 API 참조에서 /api/docs 링크를 연다.</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>1. Swagger 화면에 API 목록이 보인다(빈 화면이 아니다).</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -16899,7 +17331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P245"/>
+  <dimension ref="A1:P252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -30291,6 +30723,385 @@
       <c r="P245" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="16" t="n">
+        <v>223</v>
+      </c>
+      <c r="B246" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-UP-001</t>
+        </is>
+      </c>
+      <c r="C246" s="16" t="inlineStr">
+        <is>
+          <t>스테이징 업로드</t>
+        </is>
+      </c>
+      <c r="D246" s="16" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="E246" s="16" t="n"/>
+      <c r="F246" s="16" t="n"/>
+      <c r="G246" s="16" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="H246" s="17" t="inlineStr">
+        <is>
+          <t>사용자 A 가 발급받은 upload_id</t>
+        </is>
+      </c>
+      <c r="I246" s="17" t="inlineStr">
+        <is>
+          <t>1. 사용자 B 로 그 upload_id 를 가져오기에 보낸다.
+2. A 로 같은 id 를 두 번 적용한다.</t>
+        </is>
+      </c>
+      <c r="J246" s="17" t="inlineStr">
+        <is>
+          <t>1. 403
+2. 두 번째는 409</t>
+        </is>
+      </c>
+      <c r="K246" s="37" t="n"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="16" t="n">
+        <v>224</v>
+      </c>
+      <c r="B247" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-UP-002</t>
+        </is>
+      </c>
+      <c r="C247" s="16" t="inlineStr">
+        <is>
+          <t>스테이징 업로드</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="inlineStr">
+        <is>
+          <t>잠금</t>
+        </is>
+      </c>
+      <c r="E247" s="16" t="n"/>
+      <c r="F247" s="16" t="n"/>
+      <c r="G247" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H247" s="17" t="inlineStr">
+        <is>
+          <t>미리보기를 마친 upload_id</t>
+        </is>
+      </c>
+      <c r="I247" s="17" t="inlineStr">
+        <is>
+          <t>1. 미리보기 응답을 받자마자 같은 id 로 가져오기를 보낸다.</t>
+        </is>
+      </c>
+      <c r="J247" s="17" t="inlineStr">
+        <is>
+          <t>1. 201. 미리보기가 잡은 잠금이 응답 전에 풀려 409 가 나지 않는다.</t>
+        </is>
+      </c>
+      <c r="K247" s="37" t="n"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="16" t="n">
+        <v>225</v>
+      </c>
+      <c r="B248" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-LOCK-001</t>
+        </is>
+      </c>
+      <c r="C248" s="16" t="inlineStr">
+        <is>
+          <t>동시성</t>
+        </is>
+      </c>
+      <c r="D248" s="16" t="inlineStr">
+        <is>
+          <t>TC 복제</t>
+        </is>
+      </c>
+      <c r="E248" s="16" t="n"/>
+      <c r="F248" s="16" t="n"/>
+      <c r="G248" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H248" s="17" t="inlineStr">
+        <is>
+          <t>TC 가 있는 프로젝트</t>
+        </is>
+      </c>
+      <c r="I248" s="17" t="inlineStr">
+        <is>
+          <t>1. 같은 프로젝트에서 TC 복제 요청 8개를 동시에 보낸다.</t>
+        </is>
+      </c>
+      <c r="J248" s="17" t="inlineStr">
+        <is>
+          <t>1. 전부 201 이고 TC 번호가 겹치지 않는다.</t>
+        </is>
+      </c>
+      <c r="K248" s="37" t="n"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="16" t="n">
+        <v>226</v>
+      </c>
+      <c r="B249" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-MIG-001</t>
+        </is>
+      </c>
+      <c r="C249" s="16" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="inlineStr">
+        <is>
+          <t>사전 점검</t>
+        </is>
+      </c>
+      <c r="E249" s="16" t="n"/>
+      <c r="F249" s="16" t="n"/>
+      <c r="G249" s="16" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="H249" s="17" t="inlineStr">
+        <is>
+          <t>v1.10.3.1 SQLite 사본, 빈 PostgreSQL(alembic head)</t>
+        </is>
+      </c>
+      <c r="I249" s="17" t="inlineStr">
+        <is>
+          <t>1. scripts/migrate_sqlite_to_pg.py --dry-run 을 실행한다.
+2. 허용하지 않은 FK 고아가 있는 사본으로 실행한다.</t>
+        </is>
+      </c>
+      <c r="J249" s="17" t="inlineStr">
+        <is>
+          <t>1. 종료코드 0, 대상은 비어 있다.
+2. 종료코드 1, 고아 목록이 나오고 대상에 아무것도 쓰지 않는다.</t>
+        </is>
+      </c>
+      <c r="K249" s="37" t="n"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="16" t="n">
+        <v>227</v>
+      </c>
+      <c r="B250" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-MIG-002</t>
+        </is>
+      </c>
+      <c r="C250" s="16" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="D250" s="16" t="inlineStr">
+        <is>
+          <t>값 보존</t>
+        </is>
+      </c>
+      <c r="E250" s="16" t="n"/>
+      <c r="F250" s="16" t="n"/>
+      <c r="G250" s="16" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="H250" s="17" t="inlineStr">
+        <is>
+          <t>custom_fields 에 SQL NULL, 텍스트 'null', 객체가 섞인 사본</t>
+        </is>
+      </c>
+      <c r="I250" s="17" t="inlineStr">
+        <is>
+          <t>1. 이관을 실행한다.
+2. json_typeof(custom_fields) 를 본다.</t>
+        </is>
+      </c>
+      <c r="J250" s="17" t="inlineStr">
+        <is>
+          <t>1. 독립 검증 불일치 0.
+2. 각각 NULL, null, object 로 남는다(이중 인코딩 없음).</t>
+        </is>
+      </c>
+      <c r="K250" s="37" t="n"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="16" t="n">
+        <v>228</v>
+      </c>
+      <c r="B251" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-MIG-003</t>
+        </is>
+      </c>
+      <c r="C251" s="16" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="inlineStr">
+        <is>
+          <t>첨부</t>
+        </is>
+      </c>
+      <c r="E251" s="16" t="n"/>
+      <c r="F251" s="16" t="n"/>
+      <c r="G251" s="16" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="H251" s="17" t="inlineStr">
+        <is>
+          <t>첨부 행 1건, DB 행 없는 파일이 있는 uploads</t>
+        </is>
+      </c>
+      <c r="I251" s="17" t="inlineStr">
+        <is>
+          <t>1. 이관을 실행한다.
+2. --attachments-only 로 다시 실행한다.</t>
+        </is>
+      </c>
+      <c r="J251" s="17" t="inlineStr">
+        <is>
+          <t>1. 첨부가 attachments/ 키로 올라가고 해시가 같다. 행 없는 파일은 목록만 나온다.
+2. 건너뛴다.</t>
+        </is>
+      </c>
+      <c r="K251" s="37" t="n"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="16" t="n">
+        <v>229</v>
+      </c>
+      <c r="B252" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-MIG-004</t>
+        </is>
+      </c>
+      <c r="C252" s="16" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="D252" s="16" t="inlineStr">
+        <is>
+          <t>응답 비교</t>
+        </is>
+      </c>
+      <c r="E252" s="16" t="n"/>
+      <c r="F252" s="16" t="n"/>
+      <c r="G252" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H252" s="17" t="inlineStr">
+        <is>
+          <t>이관 전 SQLite 서버와 이관 후 PostgreSQL 서버</t>
+        </is>
+      </c>
+      <c r="I252" s="17" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 목록, 대시보드 7종, 리포트를 양쪽에서 받아 비교한다.</t>
+        </is>
+      </c>
+      <c r="J252" s="17" t="inlineStr">
+        <is>
+          <t>1. 응답이 같다(리포트 분류 순서 포함).</t>
+        </is>
+      </c>
+      <c r="K252" s="37" t="n"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P270"/>
+  <dimension ref="A1:P279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -17291,6 +17291,563 @@
         </is>
       </c>
       <c r="P270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>243</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>TC-AUTH-013</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>이메일 로그인</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>이메일로 가입해 승인된 계정</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>1. 로그인 칸에 이메일을 대소문자를 섞어 입력한다(예: Ym@Example.com).
+2. 비밀번호를 넣고 로그인한다.</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>1. 로그인된다(이메일은 대소문자를 가리지 않는다).</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>244</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TC-AUTH-014</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Google 버튼</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>GOOGLE_CLIENT_ID 가 설정된 서버</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>1. 로그인 화면을 연다.
+2. 'Google 로 로그인' 을 누른다.</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>1. 버튼이 보인다(클라이언트 ID 가 없으면 보이지 않는다).
+2. Google 계정 선택 화면으로 넘어간다.</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>245</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TC-AUTH-015</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>승인 대기 안내</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>AUTH_APPROVAL=personal 서버, 이메일로 가입한 계정</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>1. 승인 전에 그 계정으로 로그인한다.
+2. 틀린 비밀번호로도 로그인해 본다.</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>1. '관리자 승인을 기다리는 중입니다.' 가 보인다.
+2. 비밀번호가 틀리면 일반 실패 문구만 보인다.</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>246</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>TC-AUTH-016</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>회원가입</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>첫 관리자</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>사용자가 한 명도 없는 DB</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>1. 가입 화면을 연다.</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>1. 제목이 '관리자 계정 만들기' 이고 아이디 칸과 설치 토큰 칸이 있다.
+2. 운영 환경에서는 토큰이 맞아야 만들어진다.</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>247</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>TC-AUTH-017</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>회원가입</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>이메일 가입</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>사용자가 있는 DB</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1. 가입 화면에서 이메일, 이름, 비밀번호로 가입한다.</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>1. 아이디 칸 대신 이메일 칸이 있다.
+2. 승인이 필요한 설정이면 '가입 신청이 접수됐습니다...' 안내가 보인다.</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>248</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>TC-AUTH-018</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>계정 연결</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Google 연결과 해제</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>아이디로 로그인한 사용자, Google 로그인이 켜진 서버</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>1. 사용자 메뉴 &gt; 계정 연결 &gt; Google 계정 연결.
+2. Google 에서 계정을 고르고 돌아온다.
+3. 다시 계정 연결 창에서 연결 해제한다.</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>1. 'Google 계정을 연결했습니다.' 가 보이고 그 뒤 Google 로그인으로 같은 계정에 들어온다.
+2. 비밀번호가 없는 계정은 해제 버튼 대신 안내가 보인다.</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>249</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TC-ADM-008</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>사용자 관리</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>가입 승인</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>승인 대기 계정이 있는 상태</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>1. 관리 화면을 연다.
+2. 승인 대기 계정을 승인한다. 다른 계정은 거절한다.</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>1. 목록 위에 '승인 대기 N명' 이 보인다.
+2. 승인한 계정은 로그인되고, 거절한 계정은 목록에서 사라진다.</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>250</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>TC-ADM-009</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>사용자 관리</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>사용 중지</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>로그인해 있는 일반 사용자</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>1. 그 사용자를 사용 중지한다.
+2. 그 사용자 화면을 새로고침한다.
+3. 다시 사용으로 되돌린다.</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>1. 그 사용자는 로그인 화면으로 간다.
+2. 다시 사용해도 중지 전 API 키는 쓸 수 없다.
+3. 자기 자신과 마지막 관리자에는 사용 중지 버튼이 없거나 거절된다.</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>251</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TC-ADM-010</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>사용자 관리</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>이메일 해제</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>확인 안 된 이메일로 가입한 계정</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>1. 그 계정의 '이메일 해제' 를 누른다.</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>1. 이메일 칸이 비고, 같은 주소의 Google 로그인이 새 계정을 만들 수 있다.
+2. Google 이 확인한 이메일에는 버튼이 없다.</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -17331,7 +17888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P252"/>
+  <dimension ref="A1:P258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -31102,6 +31659,356 @@
       <c r="P252" t="inlineStr">
         <is>
           <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="B253" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-007</t>
+        </is>
+      </c>
+      <c r="C253" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D253" s="16" t="inlineStr">
+        <is>
+          <t>정책 판정</t>
+        </is>
+      </c>
+      <c r="E253" s="16" t="n"/>
+      <c r="F253" s="16" t="n"/>
+      <c r="G253" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H253" s="17" t="inlineStr">
+        <is>
+          <t>AUTH_APPROVAL x AUTH_ALLOW_PERSONAL 조합</t>
+        </is>
+      </c>
+      <c r="I253" s="17" t="inlineStr">
+        <is>
+          <t>1. 회사 Google, 개인 Google, 회사 도메인 이메일, 기타 이메일 가입의 상태를 본다.</t>
+        </is>
+      </c>
+      <c r="J253" s="17" t="inlineStr">
+        <is>
+          <t>1. 판정표(설계 문서)와 같다. 회사 계정만 설정에서 이메일 가입은 항상 승인 대기.</t>
+        </is>
+      </c>
+      <c r="K253" s="37" t="n"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="16" t="n">
+        <v>231</v>
+      </c>
+      <c r="B254" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-008</t>
+        </is>
+      </c>
+      <c r="C254" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D254" s="16" t="inlineStr">
+        <is>
+          <t>Google 콜백</t>
+        </is>
+      </c>
+      <c r="E254" s="16" t="n"/>
+      <c r="F254" s="16" t="n"/>
+      <c r="G254" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H254" s="17" t="inlineStr">
+        <is>
+          <t>Google 응답을 가짜로 바꾼 테스트</t>
+        </is>
+      </c>
+      <c r="I254" s="17" t="inlineStr">
+        <is>
+          <t>1. state 불일치, nonce 불일치, 이메일 미확인, 사이트 밖 next, 취소를 보낸다.</t>
+        </is>
+      </c>
+      <c r="J254" s="17" t="inlineStr">
+        <is>
+          <t>1. 각각 정해진 오류 코드로 로그인 화면에 돌아오고 계정이 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="K254" s="37" t="n"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="16" t="n">
+        <v>232</v>
+      </c>
+      <c r="B255" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-009</t>
+        </is>
+      </c>
+      <c r="C255" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D255" s="16" t="inlineStr">
+        <is>
+          <t>동시성</t>
+        </is>
+      </c>
+      <c r="E255" s="16" t="n"/>
+      <c r="F255" s="16" t="n"/>
+      <c r="G255" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H255" s="17" t="inlineStr">
+        <is>
+          <t>독립 세션 동시 요청</t>
+        </is>
+      </c>
+      <c r="I255" s="17" t="inlineStr">
+        <is>
+          <t>1. 첫 관리자 동시 가입(IP 다름), 관리자 상호 중지·강등, 같은 Google 계정 동시 첫 로그인.</t>
+        </is>
+      </c>
+      <c r="J255" s="17" t="inlineStr">
+        <is>
+          <t>1. 관리자 한 명, 활성 관리자 최소 한 명, 계정 하나가 남는다.</t>
+        </is>
+      </c>
+      <c r="K255" s="37" t="n"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="16" t="n">
+        <v>233</v>
+      </c>
+      <c r="B256" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-010</t>
+        </is>
+      </c>
+      <c r="C256" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D256" s="16" t="inlineStr">
+        <is>
+          <t>사용 중지 효력</t>
+        </is>
+      </c>
+      <c r="E256" s="16" t="n"/>
+      <c r="F256" s="16" t="n"/>
+      <c r="G256" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H256" s="17" t="inlineStr">
+        <is>
+          <t>API 키가 있는 사용자</t>
+        </is>
+      </c>
+      <c r="I256" s="17" t="inlineStr">
+        <is>
+          <t>1. 사용 중지 후 기존 JWT 와 API 키로 요청한다.
+2. 다시 사용 후 옛 키로 요청한다.</t>
+        </is>
+      </c>
+      <c r="J256" s="17" t="inlineStr">
+        <is>
+          <t>1. 둘 다 401.
+2. 옛 키는 계속 401.</t>
+        </is>
+      </c>
+      <c r="K256" s="37" t="n"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="16" t="n">
+        <v>234</v>
+      </c>
+      <c r="B257" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-011</t>
+        </is>
+      </c>
+      <c r="C257" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="inlineStr">
+        <is>
+          <t>로그인 횟수 제한</t>
+        </is>
+      </c>
+      <c r="E257" s="16" t="n"/>
+      <c r="F257" s="16" t="n"/>
+      <c r="G257" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H257" s="17" t="inlineStr">
+        <is>
+          <t>이메일 계정</t>
+        </is>
+      </c>
+      <c r="I257" s="17" t="inlineStr">
+        <is>
+          <t>1. 대소문자를 바꿔 가며 틀린 비밀번호를 11번 보낸다.</t>
+        </is>
+      </c>
+      <c r="J257" s="17" t="inlineStr">
+        <is>
+          <t>1. 11번째가 429(같은 제한 키로 묶인다).</t>
+        </is>
+      </c>
+      <c r="K257" s="37" t="n"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="16" t="n">
+        <v>235</v>
+      </c>
+      <c r="B258" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-012</t>
+        </is>
+      </c>
+      <c r="C258" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D258" s="16" t="inlineStr">
+        <is>
+          <t>마이그레이션 0007</t>
+        </is>
+      </c>
+      <c r="E258" s="16" t="n"/>
+      <c r="F258" s="16" t="n"/>
+      <c r="G258" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H258" s="17" t="inlineStr">
+        <is>
+          <t>0006 상태의 DB</t>
+        </is>
+      </c>
+      <c r="I258" s="17" t="inlineStr">
+        <is>
+          <t>1. 0007 로 올린다. 내렸다 다시 올린다.</t>
+        </is>
+      </c>
+      <c r="J258" s="17" t="inlineStr">
+        <is>
+          <t>1. 기존 사용자는 active, 비밀번호 없는 행을 넣을 수 있고, 복구 이력이 사용자 삭제를 막지 않는다.</t>
+        </is>
+      </c>
+      <c r="K258" s="37" t="n"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P279"/>
+  <dimension ref="A1:P282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -17792,7 +17792,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" s="50">
       <c r="A279" t="n">
         <v>251</v>
       </c>
@@ -17850,6 +17850,196 @@
       <c r="P279" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" s="50">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TC-ADM-011</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>사용자 관리</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>빈 계정 삭제</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>작업 기록이 없는 다른 사용자 계정</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>1. 그 계정의 '삭제' 를 누르고 확인한다.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>1. '삭제했습니다.' 가 보이고 행이 사라진다.
+2. 본인 행과 승인 대기 행에는 '삭제' 가 없다.</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" s="50">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TC-ADM-012</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>사용자 관리</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>연결된 Google 계정 표시</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Google 이 연결된 사용자</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>1. 사용자 관리 표의 로그인 방식 칸을 본다.</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>1. 'Google: &lt;주소&gt;' 가 보인다.
+2. 이 기능 전에 연결된 계정은 'Google: 주소 미기록' 이고, 다음 Google 로그인 뒤 주소가 채워진다.</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" s="50">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TC-AUTH-019</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>계정 연결</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>빈 Google 계정 정리 후 연결</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Google 로그인으로 실수로 만든 빈 계정(비밀번호 없음, 기록 없음)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>1. 아이디로 로그인한다.
+2. 사용자 메뉴 &gt; 계정 연결 &gt; Google 계정 연결에서 같은 Google 계정을 고른다.</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>1. '빈 계정은 정리했습니다' 알림이 보인다.
+2. 사용자 관리 표에서 빈 계정이 사라지고 이 계정에 Google 주소가 보인다. 이 계정에 이메일이 없었으면 이메일도 옮겨진다.</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -17888,7 +18078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P258"/>
+  <dimension ref="A1:P262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -31954,7 +32144,7 @@
         </is>
       </c>
     </row>
-    <row r="258">
+    <row r="258" s="50">
       <c r="A258" s="16" t="n">
         <v>235</v>
       </c>
@@ -32007,6 +32197,248 @@
         </is>
       </c>
       <c r="P258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" s="50">
+      <c r="A259" s="16" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="B259" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-013</t>
+        </is>
+      </c>
+      <c r="C259" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D259" s="16" t="inlineStr">
+        <is>
+          <t>계정 삭제</t>
+        </is>
+      </c>
+      <c r="E259" s="16" t="n"/>
+      <c r="F259" s="16" t="n"/>
+      <c r="G259" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H259" s="17" t="inlineStr">
+        <is>
+          <t>관리자 세션</t>
+        </is>
+      </c>
+      <c r="I259" s="17" t="inlineStr">
+        <is>
+          <t>1. DELETE /api/auth/users/{id} 를 기록 없는 계정, 기록 있는 계정, 본인, 없는 id 로 부른다.</t>
+        </is>
+      </c>
+      <c r="J259" s="17" t="inlineStr">
+        <is>
+          <t>1. 204 / 409(사용 중지 안내) / 409 / 404. 일반 사용자 403, 비로그인 401.</t>
+        </is>
+      </c>
+      <c r="K259" s="37" t="n"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" s="50">
+      <c r="A260" s="16" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="B260" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-014</t>
+        </is>
+      </c>
+      <c r="C260" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D260" s="16" t="inlineStr">
+        <is>
+          <t>Google 연결 시 빈 계정 정리</t>
+        </is>
+      </c>
+      <c r="E260" s="16" t="n"/>
+      <c r="F260" s="16" t="n"/>
+      <c r="G260" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H260" s="17" t="inlineStr">
+        <is>
+          <t>같은 Google 계정에 묶인 다른 계정</t>
+        </is>
+      </c>
+      <c r="I260" s="17" t="inlineStr">
+        <is>
+          <t>1. 그 계정이 비밀번호 없음·기록 없음이면 연결을 시도한다(승인 대기, 사용 중지 포함).
+2. 비밀번호나 기록(API 키 포함)이 있거나 마지막 활성 관리자면 연결을 시도한다.</t>
+        </is>
+      </c>
+      <c r="J260" s="17" t="inlineStr">
+        <is>
+          <t>1. account=merged, 빈 계정 삭제, Google 주소가 옮겨지고 이메일은 현재 계정에 이메일이 없을 때만 옮겨진다.
+2. account=already_linked, 아무것도 바뀌지 않는다.</t>
+        </is>
+      </c>
+      <c r="K260" s="37" t="n"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" s="50">
+      <c r="A261" s="16" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B261" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-015</t>
+        </is>
+      </c>
+      <c r="C261" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D261" s="16" t="inlineStr">
+        <is>
+          <t>연결된 Google 주소 기록</t>
+        </is>
+      </c>
+      <c r="E261" s="16" t="n"/>
+      <c r="F261" s="16" t="n"/>
+      <c r="G261" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H261" s="17" t="inlineStr">
+        <is>
+          <t>Google 로그인이 켜진 서버</t>
+        </is>
+      </c>
+      <c r="I261" s="17" t="inlineStr">
+        <is>
+          <t>1. Google 신규 가입, 기존 연결 계정 로그인, 이메일이 선점된 상태의 연결, 해제, 관리자 초기화, 계정 복구를 한다.</t>
+        </is>
+      </c>
+      <c r="J261" s="17" t="inlineStr">
+        <is>
+          <t>1. google_email 이 가입·로그인·연결 때 최신 주소로 남고, 해제·초기화·복구 때 지워진다.</t>
+        </is>
+      </c>
+      <c r="K261" s="37" t="n"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" s="50">
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B262" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-AUTH-016</t>
+        </is>
+      </c>
+      <c r="C262" s="16" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D262" s="16" t="inlineStr">
+        <is>
+          <t>마이그레이션 0008</t>
+        </is>
+      </c>
+      <c r="E262" s="16" t="n"/>
+      <c r="F262" s="16" t="n"/>
+      <c r="G262" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H262" s="17" t="inlineStr">
+        <is>
+          <t>0007 상태의 DB</t>
+        </is>
+      </c>
+      <c r="I262" s="17" t="inlineStr">
+        <is>
+          <t>1. 0008 로 올린다. 내렸다 다시 올린다.</t>
+        </is>
+      </c>
+      <c r="J262" s="17" t="inlineStr">
+        <is>
+          <t>1. 기존 연결 계정의 google_email 은 비어 있고, 왕복해도 오류가 없다.</t>
+        </is>
+      </c>
+      <c r="K262" s="37" t="n"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
